--- a/drivers/xlsx/testdata/actor_no_header.xlsx
+++ b/drivers/xlsx/testdata/actor_no_header.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="250">
   <si>
-    <t>2020-02-15T06:59:28Z</t>
+    <t>2006-02-15T04:34:33Z</t>
   </si>
   <si>
     <t>MARY</t>
